--- a/docs/downloads/09/t8_transition_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/09/t8_transition_alaotra_ambodivoara.xlsx
@@ -443,12 +443,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>5.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -465,12 +459,6 @@
         <is>
           <t>Maïs</t>
         </is>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>5.2</v>
       </c>
     </row>
     <row r="6">
